--- a/events/Bratislava_2021_WWC/Bratislava_2021_WWC_start.xlsx
+++ b/events/Bratislava_2021_WWC/Bratislava_2021_WWC_start.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W324"/>
+  <dimension ref="A1:AC319"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,17 +519,47 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Name4</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Name5</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Name6</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
           <t>ICF_ID1</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>ICF_ID2</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>ICF_ID3</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>ICF_ID4</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>ICF_ID5</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>ICF_ID6</t>
         </is>
       </c>
     </row>
@@ -580,11 +610,6 @@
       <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Forerunner 1</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -663,17 +688,17 @@
           <t>HOCEVAR Simeon</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>83918</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>93891</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>36273</t>
         </is>
@@ -756,17 +781,17 @@
           <t>IVANECKY Jaromir</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>82996</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>98676</t>
         </is>
@@ -849,17 +874,17 @@
           <t>QUINTARELLI Mattia</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>75796</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>75795</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>39775</t>
         </is>
@@ -942,17 +967,17 @@
           <t>TOLIC Ivan</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>39640</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>39639</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>39671</t>
         </is>
@@ -1035,17 +1060,17 @@
           <t>HALES Antonin</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>35512</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>35516</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="Z7" t="inlineStr">
         <is>
           <t>35515</t>
         </is>
@@ -1128,17 +1153,17 @@
           <t>FERRION Charles</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>63173</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>56165</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>94783</t>
         </is>
@@ -1221,17 +1246,17 @@
           <t>DOMAJNKO Helena</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>94495</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>83919</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="Z9" t="inlineStr">
         <is>
           <t>83895</t>
         </is>
@@ -1314,17 +1339,17 @@
           <t>POLONYOVA Tereza</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>35471</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="Z10" t="inlineStr">
         <is>
           <t>98690</t>
         </is>
@@ -1407,17 +1432,17 @@
           <t>DONATELLI Valeria</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>75522</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>39777</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>75797</t>
         </is>
@@ -1500,17 +1525,17 @@
           <t>ECKERT Jil-Sophie</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>87895</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>64811</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="Z12" t="inlineStr">
         <is>
           <t>39763</t>
         </is>
@@ -1593,17 +1618,17 @@
           <t>DUPRAS Phenicia</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>75974</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>53291</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>56152</t>
         </is>
@@ -1686,17 +1711,17 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>63231</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>78808</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -1769,17 +1794,17 @@
           <t>DIMITRIJEVIC Ognjen</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>43084</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>87291</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>39961</t>
         </is>
@@ -1852,17 +1877,17 @@
           <t>WINKLER Paul</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>75626</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="Y16" t="inlineStr">
         <is>
           <t>46839</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="Z16" t="inlineStr">
         <is>
           <t>105625</t>
         </is>
@@ -1945,17 +1970,17 @@
           <t>MACUS Ondrej</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>36674</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="Y17" t="inlineStr">
         <is>
           <t>96068</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>94095</t>
         </is>
@@ -2038,17 +2063,17 @@
           <t>BERNARDI Andrea</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>70132</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>94769</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>63276</t>
         </is>
@@ -2131,17 +2156,17 @@
           <t>JEFFERIES Robert</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>53139</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="Y19" t="inlineStr">
         <is>
           <t>79368</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="Z19" t="inlineStr">
         <is>
           <t>53202</t>
         </is>
@@ -2224,17 +2249,17 @@
           <t>FENGLER Till</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>37662</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>45115</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>95456</t>
         </is>
@@ -2317,17 +2342,17 @@
           <t>MATEJICEK Vojtech</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>43285</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>70681</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>87966</t>
         </is>
@@ -2410,17 +2435,17 @@
           <t>MORET Hugues</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="X22" t="inlineStr">
         <is>
           <t>94780</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr">
+      <c r="Y22" t="inlineStr">
         <is>
           <t>45024</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="Z22" t="inlineStr">
         <is>
           <t>56142</t>
         </is>
@@ -2503,17 +2528,17 @@
           <t>OVEN Simon</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="X23" t="inlineStr">
         <is>
           <t>37764</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr">
+      <c r="Y23" t="inlineStr">
         <is>
           <t>44341</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
+      <c r="Z23" t="inlineStr">
         <is>
           <t>38164</t>
         </is>
@@ -2596,17 +2621,17 @@
           <t>RAGUENES Helene</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="X24" t="inlineStr">
         <is>
           <t>76817</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr">
+      <c r="Y24" t="inlineStr">
         <is>
           <t>98758</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="Z24" t="inlineStr">
         <is>
           <t>76819</t>
         </is>
@@ -2676,17 +2701,62 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>SUCHANEK Daniel/ROLENC Ondrej</t>
+          <t>SUCHANEK Daniel</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>RYGEL Marek/VESELY Petr</t>
+          <t>ROLENC Ondrej</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>TOMEK Lukas/SRAMEK Michal</t>
+          <t>RYGEL Marek</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>VESELY Petr</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>TOMEK Lukas</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>SRAMEK Michal</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>42246</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>35512</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>53303</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>35511</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>35505</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>35504</t>
         </is>
       </c>
     </row>
@@ -2754,17 +2824,62 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>TROUBADY Pierre/MORET Hugues</t>
+          <t>TROUBADY Pierre</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>GOURJAULT Ancelin/SAUTEUR Nicolas</t>
+          <t>MORET Hugues</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>SANTAMARIA Stephane/DAZEUR Quentin</t>
+          <t>GOURJAULT Ancelin</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SAUTEUR Nicolas</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>SANTAMARIA Stephane</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>DAZEUR Quentin</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>39643</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>56142</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>56131</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>63173</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>36791</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>43141</t>
         </is>
       </c>
     </row>
@@ -2883,7 +2998,7 @@
           <t>SOMMERNES Iris</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="X28" t="inlineStr">
         <is>
           <t>90378</t>
         </is>
@@ -2946,7 +3061,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="X29" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -3009,7 +3124,7 @@
           <t>NOBIS Constanza</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="X30" t="inlineStr">
         <is>
           <t>80605</t>
         </is>
@@ -3072,7 +3187,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="X31" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -3135,7 +3250,7 @@
           <t>MAENPAA Iisa</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="X32" t="inlineStr">
         <is>
           <t>72267</t>
         </is>
@@ -3198,7 +3313,7 @@
           <t>POLONYOVA Tereza</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="X33" t="inlineStr">
         <is>
           <t>98690</t>
         </is>
@@ -3261,7 +3376,7 @@
           <t>CREEK Amanda</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="X34" t="inlineStr">
         <is>
           <t>77289</t>
         </is>
@@ -3324,7 +3439,7 @@
           <t>KOPUNOVA Katarina</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="X35" t="inlineStr">
         <is>
           <t>35471</t>
         </is>
@@ -3387,7 +3502,7 @@
           <t>DEGLIN Sandrine</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="X36" t="inlineStr">
         <is>
           <t>104487</t>
         </is>
@@ -3450,7 +3565,7 @@
           <t>WEGMAN Martina</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="X37" t="inlineStr">
         <is>
           <t>35345</t>
         </is>
@@ -3513,7 +3628,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="X38" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -3576,7 +3691,7 @@
           <t>FEINE Constanze</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>93970</t>
         </is>
@@ -3639,7 +3754,7 @@
           <t>DOMAJNKO Helena</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="X40" t="inlineStr">
         <is>
           <t>83895</t>
         </is>
@@ -3702,7 +3817,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="X41" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -3765,7 +3880,7 @@
           <t>NEMCOVA Marie</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="X42" t="inlineStr">
         <is>
           <t>78808</t>
         </is>
@@ -3828,7 +3943,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="X43" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -3891,7 +4006,7 @@
           <t>KOSTLE Elisabeth</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="X44" t="inlineStr">
         <is>
           <t>64811</t>
         </is>
@@ -3954,7 +4069,7 @@
           <t>MASSINI Christina</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>87895</t>
         </is>
@@ -4017,7 +4132,7 @@
           <t>DIMOVOVA Barbora</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="X46" t="inlineStr">
         <is>
           <t>63231</t>
         </is>
@@ -4080,7 +4195,7 @@
           <t>MILNE Laura</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="X47" t="inlineStr">
         <is>
           <t>75768</t>
         </is>
@@ -4143,7 +4258,7 @@
           <t>JANCAR Ziva</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="X48" t="inlineStr">
         <is>
           <t>83919</t>
         </is>
@@ -4206,7 +4321,7 @@
           <t>DONATELLI Valeria</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="X49" t="inlineStr">
         <is>
           <t>75797</t>
         </is>
@@ -4269,7 +4384,7 @@
           <t>PANATO Cecilia</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="X50" t="inlineStr">
         <is>
           <t>75522</t>
         </is>
@@ -4332,7 +4447,7 @@
           <t>STEBLAJ Ana</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="X51" t="inlineStr">
         <is>
           <t>94495</t>
         </is>
@@ -4395,7 +4510,7 @@
           <t>FRESLON Pauline</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="X52" t="inlineStr">
         <is>
           <t>75974</t>
         </is>
@@ -4458,7 +4573,7 @@
           <t>VALDENAIRE Mathilde</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="X53" t="inlineStr">
         <is>
           <t>94782</t>
         </is>
@@ -4521,7 +4636,7 @@
           <t>DREIER Valentina</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="X54" t="inlineStr">
         <is>
           <t>41612</t>
         </is>
@@ -4584,7 +4699,7 @@
           <t>MUELLER Hannah</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="X55" t="inlineStr">
         <is>
           <t>63133</t>
         </is>
@@ -4647,7 +4762,7 @@
           <t>ECKERT Jil-Sophie</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="X56" t="inlineStr">
         <is>
           <t>39763</t>
         </is>
@@ -4710,7 +4825,7 @@
           <t>ROSA Mathilde Serena</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>39777</t>
         </is>
@@ -4773,7 +4888,7 @@
           <t>VINET Lise</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="X58" t="inlineStr">
         <is>
           <t>53291</t>
         </is>
@@ -4836,7 +4951,7 @@
           <t>DUPRAS Phenicia</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="X59" t="inlineStr">
         <is>
           <t>56152</t>
         </is>
@@ -4899,7 +5014,7 @@
           <t>QUINTARELLI Federico</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="X60" t="inlineStr">
         <is>
           <t>75789</t>
         </is>
@@ -4962,7 +5077,7 @@
           <t>PEREIRA MACHADO Luiz Antonio</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="X61" t="inlineStr">
         <is>
           <t>113696</t>
         </is>
@@ -5025,7 +5140,7 @@
           <t>AVERSA Pedro</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
@@ -5088,7 +5203,7 @@
           <t>IVANECKY Jaromir</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>98676</t>
         </is>
@@ -5151,7 +5266,7 @@
           <t>GALE Martin</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="X64" t="inlineStr">
         <is>
           <t>93891</t>
         </is>
@@ -5214,7 +5329,7 @@
           <t>HALES Antonin</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="X65" t="inlineStr">
         <is>
           <t>35515</t>
         </is>
@@ -5277,7 +5392,7 @@
           <t>HOCEVAR Simeon</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="X66" t="inlineStr">
         <is>
           <t>36273</t>
         </is>
@@ -5340,7 +5455,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="X67" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -5403,7 +5518,7 @@
           <t>ZONJIC Jadran</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="X68" t="inlineStr">
         <is>
           <t>39640</t>
         </is>
@@ -5466,7 +5581,7 @@
           <t>DANIK Ladislav</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="X69" t="inlineStr">
         <is>
           <t>82996</t>
         </is>
@@ -5529,7 +5644,7 @@
           <t>QUINTARELLI Mattia</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="X70" t="inlineStr">
         <is>
           <t>39775</t>
         </is>
@@ -5592,7 +5707,7 @@
           <t>SCHWARZ Ole</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="X71" t="inlineStr">
         <is>
           <t>76065</t>
         </is>
@@ -5655,7 +5770,7 @@
           <t>TOLIC Ivan</t>
         </is>
       </c>
-      <c r="U72" t="inlineStr">
+      <c r="X72" t="inlineStr">
         <is>
           <t>39671</t>
         </is>
@@ -5718,7 +5833,7 @@
           <t>ROLENC Ondrej</t>
         </is>
       </c>
-      <c r="U73" t="inlineStr">
+      <c r="X73" t="inlineStr">
         <is>
           <t>35512</t>
         </is>
@@ -5781,7 +5896,7 @@
           <t>GRADISEK Nejc</t>
         </is>
       </c>
-      <c r="U74" t="inlineStr">
+      <c r="X74" t="inlineStr">
         <is>
           <t>83918</t>
         </is>
@@ -5844,7 +5959,7 @@
           <t>ZDRAVKOVIC Pavle</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="X75" t="inlineStr">
         <is>
           <t>39964</t>
         </is>
@@ -5907,7 +6022,7 @@
           <t>BIANCHETTI Giacomo</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="X76" t="inlineStr">
         <is>
           <t>75796</t>
         </is>
@@ -5970,7 +6085,7 @@
           <t>VANEK Matej</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="X77" t="inlineStr">
         <is>
           <t>98305</t>
         </is>
@@ -6033,7 +6148,7 @@
           <t>MAPELLI Tommaso</t>
         </is>
       </c>
-      <c r="U78" t="inlineStr">
+      <c r="X78" t="inlineStr">
         <is>
           <t>75795</t>
         </is>
@@ -6096,7 +6211,7 @@
           <t>FERRION Charles</t>
         </is>
       </c>
-      <c r="U79" t="inlineStr">
+      <c r="X79" t="inlineStr">
         <is>
           <t>94783</t>
         </is>
@@ -6159,7 +6274,7 @@
           <t>KLATT Etienne</t>
         </is>
       </c>
-      <c r="U80" t="inlineStr">
+      <c r="X80" t="inlineStr">
         <is>
           <t>56165</t>
         </is>
@@ -6222,7 +6337,7 @@
           <t>OBADIC Luka</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="X81" t="inlineStr">
         <is>
           <t>39639</t>
         </is>
@@ -6285,7 +6400,7 @@
           <t>SAUTEUR Nicolas</t>
         </is>
       </c>
-      <c r="U82" t="inlineStr">
+      <c r="X82" t="inlineStr">
         <is>
           <t>63173</t>
         </is>
@@ -6348,7 +6463,7 @@
           <t>DAZEUR Quentin</t>
         </is>
       </c>
-      <c r="U83" t="inlineStr">
+      <c r="X83" t="inlineStr">
         <is>
           <t>43141</t>
         </is>
@@ -6411,7 +6526,7 @@
           <t>SLANINA Vladimir</t>
         </is>
       </c>
-      <c r="U84" t="inlineStr">
+      <c r="X84" t="inlineStr">
         <is>
           <t>35516</t>
         </is>
@@ -6474,7 +6589,7 @@
           <t>KOZMA Patrick</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
+      <c r="X85" t="inlineStr">
         <is>
           <t>104624</t>
         </is>
@@ -6537,7 +6652,7 @@
           <t>MUTURI Samuel</t>
         </is>
       </c>
-      <c r="U86" t="inlineStr">
+      <c r="X86" t="inlineStr">
         <is>
           <t>68743</t>
         </is>
@@ -6600,7 +6715,7 @@
           <t>ONG Jun Yi</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr">
+      <c r="X87" t="inlineStr">
         <is>
           <t>75421</t>
         </is>
@@ -6663,7 +6778,7 @@
           <t>BAKOVIC Ignacio</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
+      <c r="X88" t="inlineStr">
         <is>
           <t>85146</t>
         </is>
@@ -6726,7 +6841,7 @@
           <t>FENTANES Ricardo</t>
         </is>
       </c>
-      <c r="U89" t="inlineStr">
+      <c r="X89" t="inlineStr">
         <is>
           <t>94184</t>
         </is>
@@ -6789,7 +6904,7 @@
           <t>PLAUDIS Martins</t>
         </is>
       </c>
-      <c r="U90" t="inlineStr">
+      <c r="X90" t="inlineStr">
         <is>
           <t>106153</t>
         </is>
@@ -6852,7 +6967,7 @@
           <t>OLAR Matteo-Alexander</t>
         </is>
       </c>
-      <c r="U91" t="inlineStr">
+      <c r="X91" t="inlineStr">
         <is>
           <t>104625</t>
         </is>
@@ -6915,7 +7030,7 @@
           <t>RAGHAVAN Kartik</t>
         </is>
       </c>
-      <c r="U92" t="inlineStr">
+      <c r="X92" t="inlineStr">
         <is>
           <t>96666</t>
         </is>
@@ -6978,7 +7093,7 @@
           <t>DE PAULA Andre Luiz</t>
         </is>
       </c>
-      <c r="U93" t="inlineStr">
+      <c r="X93" t="inlineStr">
         <is>
           <t>93227</t>
         </is>
@@ -7041,7 +7156,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U94" t="inlineStr">
+      <c r="X94" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -7104,7 +7219,7 @@
           <t>MACUS Ondrej</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr">
+      <c r="X95" t="inlineStr">
         <is>
           <t>94095</t>
         </is>
@@ -7167,7 +7282,7 @@
           <t>HEBORT Samuel</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr">
+      <c r="X96" t="inlineStr">
         <is>
           <t>96068</t>
         </is>
@@ -7230,7 +7345,7 @@
           <t>HOLMES Jacob</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
+      <c r="X97" t="inlineStr">
         <is>
           <t>53139</t>
         </is>
@@ -7293,7 +7408,7 @@
           <t>BLODER Marcel</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
+      <c r="X98" t="inlineStr">
         <is>
           <t>46839</t>
         </is>
@@ -7356,7 +7471,7 @@
           <t>ZAPLETAL Mikulas</t>
         </is>
       </c>
-      <c r="U99" t="inlineStr">
+      <c r="X99" t="inlineStr">
         <is>
           <t>63523</t>
         </is>
@@ -7419,7 +7534,7 @@
           <t>STROUSE Garet</t>
         </is>
       </c>
-      <c r="U100" t="inlineStr">
+      <c r="X100" t="inlineStr">
         <is>
           <t>104490</t>
         </is>
@@ -7482,7 +7597,7 @@
           <t>RAJNIAK Boris</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr">
+      <c r="X101" t="inlineStr">
         <is>
           <t>37309</t>
         </is>
@@ -7545,7 +7660,7 @@
           <t>KANISCAK Kamil</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr">
+      <c r="X102" t="inlineStr">
         <is>
           <t>36674</t>
         </is>
@@ -7608,7 +7723,7 @@
           <t>JEFFERIES Robert</t>
         </is>
       </c>
-      <c r="U103" t="inlineStr">
+      <c r="X103" t="inlineStr">
         <is>
           <t>53202</t>
         </is>
@@ -7671,7 +7786,7 @@
           <t>ZAPLETAL Vojtech</t>
         </is>
       </c>
-      <c r="U104" t="inlineStr">
+      <c r="X104" t="inlineStr">
         <is>
           <t>43285</t>
         </is>
@@ -7734,7 +7849,7 @@
           <t>BOLZERN Linus</t>
         </is>
       </c>
-      <c r="U105" t="inlineStr">
+      <c r="X105" t="inlineStr">
         <is>
           <t>56069</t>
         </is>
@@ -7797,7 +7912,7 @@
           <t>WINKLER Paul</t>
         </is>
       </c>
-      <c r="U106" t="inlineStr">
+      <c r="X106" t="inlineStr">
         <is>
           <t>105625</t>
         </is>
@@ -7860,7 +7975,7 @@
           <t>DIMITRIJEVIC Ognjen</t>
         </is>
       </c>
-      <c r="U107" t="inlineStr">
+      <c r="X107" t="inlineStr">
         <is>
           <t>39961</t>
         </is>
@@ -7923,7 +8038,7 @@
           <t>KASTNER Eric</t>
         </is>
       </c>
-      <c r="U108" t="inlineStr">
+      <c r="X108" t="inlineStr">
         <is>
           <t>75626</t>
         </is>
@@ -7986,7 +8101,7 @@
           <t>FENGLER Till</t>
         </is>
       </c>
-      <c r="U109" t="inlineStr">
+      <c r="X109" t="inlineStr">
         <is>
           <t>95456</t>
         </is>
@@ -8049,7 +8164,7 @@
           <t>BARTHEL Bjoern</t>
         </is>
       </c>
-      <c r="U110" t="inlineStr">
+      <c r="X110" t="inlineStr">
         <is>
           <t>36675</t>
         </is>
@@ -8112,7 +8227,7 @@
           <t>BARONE Luca</t>
         </is>
       </c>
-      <c r="U111" t="inlineStr">
+      <c r="X111" t="inlineStr">
         <is>
           <t>94780</t>
         </is>
@@ -8175,7 +8290,7 @@
           <t>TAHIROVIC Alen</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr">
+      <c r="X112" t="inlineStr">
         <is>
           <t>87291</t>
         </is>
@@ -8238,7 +8353,7 @@
           <t>BEERSCHWENGER Bjoern</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr">
+      <c r="X113" t="inlineStr">
         <is>
           <t>37662</t>
         </is>
@@ -8301,7 +8416,7 @@
           <t>ABBIATI Giacomo</t>
         </is>
       </c>
-      <c r="U114" t="inlineStr">
+      <c r="X114" t="inlineStr">
         <is>
           <t>94769</t>
         </is>
@@ -8364,7 +8479,7 @@
           <t>BROWN Frederick</t>
         </is>
       </c>
-      <c r="U115" t="inlineStr">
+      <c r="X115" t="inlineStr">
         <is>
           <t>79368</t>
         </is>
@@ -8427,7 +8542,7 @@
           <t>HAEFELI Robin</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr">
+      <c r="X116" t="inlineStr">
         <is>
           <t>76130</t>
         </is>
@@ -8490,7 +8605,7 @@
           <t>MARJANOVIC Marko</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr">
+      <c r="X117" t="inlineStr">
         <is>
           <t>43084</t>
         </is>
@@ -8553,7 +8668,7 @@
           <t>MONTULET Leo</t>
         </is>
       </c>
-      <c r="U118" t="inlineStr">
+      <c r="X118" t="inlineStr">
         <is>
           <t>70119</t>
         </is>
@@ -8616,7 +8731,7 @@
           <t>MATEJICEK Vojtech</t>
         </is>
       </c>
-      <c r="U119" t="inlineStr">
+      <c r="X119" t="inlineStr">
         <is>
           <t>87966</t>
         </is>
@@ -8679,7 +8794,7 @@
           <t>BERNARDI Andrea</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr">
+      <c r="X120" t="inlineStr">
         <is>
           <t>63276</t>
         </is>
@@ -8742,7 +8857,7 @@
           <t>CIOTOLI Francesco</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr">
+      <c r="X121" t="inlineStr">
         <is>
           <t>70132</t>
         </is>
@@ -8805,7 +8920,7 @@
           <t>NOVAK Tim</t>
         </is>
       </c>
-      <c r="U122" t="inlineStr">
+      <c r="X122" t="inlineStr">
         <is>
           <t>55802</t>
         </is>
@@ -8868,7 +8983,7 @@
           <t>PYPE Samuel</t>
         </is>
       </c>
-      <c r="U123" t="inlineStr">
+      <c r="X123" t="inlineStr">
         <is>
           <t>54038</t>
         </is>
@@ -8931,7 +9046,7 @@
           <t>LEMMEN Yannic</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr">
+      <c r="X124" t="inlineStr">
         <is>
           <t>45115</t>
         </is>
@@ -8994,7 +9109,7 @@
           <t>OVEN Simon</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr">
+      <c r="X125" t="inlineStr">
         <is>
           <t>38164</t>
         </is>
@@ -9057,7 +9172,7 @@
           <t>SATKE Adam</t>
         </is>
       </c>
-      <c r="U126" t="inlineStr">
+      <c r="X126" t="inlineStr">
         <is>
           <t>70681</t>
         </is>
@@ -9120,7 +9235,7 @@
           <t>MORET Hugues</t>
         </is>
       </c>
-      <c r="U127" t="inlineStr">
+      <c r="X127" t="inlineStr">
         <is>
           <t>56142</t>
         </is>
@@ -9183,7 +9298,7 @@
           <t>URANKAR Anze</t>
         </is>
       </c>
-      <c r="U128" t="inlineStr">
+      <c r="X128" t="inlineStr">
         <is>
           <t>44341</t>
         </is>
@@ -9246,7 +9361,7 @@
           <t>BAROUH Maxence</t>
         </is>
       </c>
-      <c r="U129" t="inlineStr">
+      <c r="X129" t="inlineStr">
         <is>
           <t>45024</t>
         </is>
@@ -9309,7 +9424,7 @@
           <t>ZNIDARCIC Nejc</t>
         </is>
       </c>
-      <c r="U130" t="inlineStr">
+      <c r="X130" t="inlineStr">
         <is>
           <t>37764</t>
         </is>
@@ -9372,7 +9487,7 @@
           <t>CREEK Amanda</t>
         </is>
       </c>
-      <c r="U131" t="inlineStr">
+      <c r="X131" t="inlineStr">
         <is>
           <t>77289</t>
         </is>
@@ -9435,7 +9550,7 @@
           <t>PANATO Cecilia</t>
         </is>
       </c>
-      <c r="U132" t="inlineStr">
+      <c r="X132" t="inlineStr">
         <is>
           <t>75522</t>
         </is>
@@ -9498,7 +9613,7 @@
           <t>POLONYOVA Tereza</t>
         </is>
       </c>
-      <c r="U133" t="inlineStr">
+      <c r="X133" t="inlineStr">
         <is>
           <t>98690</t>
         </is>
@@ -9561,7 +9676,7 @@
           <t>NOBIS Constanza</t>
         </is>
       </c>
-      <c r="U134" t="inlineStr">
+      <c r="X134" t="inlineStr">
         <is>
           <t>80605</t>
         </is>
@@ -9624,7 +9739,7 @@
           <t>SOMMERNES Iris</t>
         </is>
       </c>
-      <c r="U135" t="inlineStr">
+      <c r="X135" t="inlineStr">
         <is>
           <t>90378</t>
         </is>
@@ -9687,7 +9802,7 @@
           <t>RAZEGHIAN Roxana</t>
         </is>
       </c>
-      <c r="U136" t="inlineStr">
+      <c r="X136" t="inlineStr">
         <is>
           <t>63124</t>
         </is>
@@ -9750,7 +9865,7 @@
           <t>MAENPAA Iisa</t>
         </is>
       </c>
-      <c r="U137" t="inlineStr">
+      <c r="X137" t="inlineStr">
         <is>
           <t>72267</t>
         </is>
@@ -9813,7 +9928,7 @@
           <t>SEPRENYI Sara Timea</t>
         </is>
       </c>
-      <c r="U138" t="inlineStr">
+      <c r="X138" t="inlineStr">
         <is>
           <t>52211</t>
         </is>
@@ -9876,7 +9991,7 @@
           <t>MASSINI Christina</t>
         </is>
       </c>
-      <c r="U139" t="inlineStr">
+      <c r="X139" t="inlineStr">
         <is>
           <t>87895</t>
         </is>
@@ -9939,7 +10054,7 @@
           <t>MACEKOVA Simona</t>
         </is>
       </c>
-      <c r="U140" t="inlineStr">
+      <c r="X140" t="inlineStr">
         <is>
           <t>45153</t>
         </is>
@@ -10002,7 +10117,7 @@
           <t>DEGLIN Sandrine</t>
         </is>
       </c>
-      <c r="U141" t="inlineStr">
+      <c r="X141" t="inlineStr">
         <is>
           <t>104487</t>
         </is>
@@ -10065,7 +10180,7 @@
           <t>DREIER Valentina</t>
         </is>
       </c>
-      <c r="U142" t="inlineStr">
+      <c r="X142" t="inlineStr">
         <is>
           <t>41612</t>
         </is>
@@ -10128,7 +10243,7 @@
           <t>FEINE Constanze</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
+      <c r="X143" t="inlineStr">
         <is>
           <t>93970</t>
         </is>
@@ -10191,7 +10306,7 @@
           <t>DONATELLI Valeria</t>
         </is>
       </c>
-      <c r="U144" t="inlineStr">
+      <c r="X144" t="inlineStr">
         <is>
           <t>75797</t>
         </is>
@@ -10254,7 +10369,7 @@
           <t>MILNE Laura</t>
         </is>
       </c>
-      <c r="U145" t="inlineStr">
+      <c r="X145" t="inlineStr">
         <is>
           <t>75768</t>
         </is>
@@ -10317,7 +10432,7 @@
           <t>JANCAR Ziva</t>
         </is>
       </c>
-      <c r="U146" t="inlineStr">
+      <c r="X146" t="inlineStr">
         <is>
           <t>83919</t>
         </is>
@@ -10380,7 +10495,7 @@
           <t>KOPUNOVA Katarina</t>
         </is>
       </c>
-      <c r="U147" t="inlineStr">
+      <c r="X147" t="inlineStr">
         <is>
           <t>35471</t>
         </is>
@@ -10443,7 +10558,7 @@
           <t>DIMOVOVA Barbora</t>
         </is>
       </c>
-      <c r="U148" t="inlineStr">
+      <c r="X148" t="inlineStr">
         <is>
           <t>63231</t>
         </is>
@@ -10506,7 +10621,7 @@
           <t>VALDENAIRE Mathilde</t>
         </is>
       </c>
-      <c r="U149" t="inlineStr">
+      <c r="X149" t="inlineStr">
         <is>
           <t>94782</t>
         </is>
@@ -10569,7 +10684,7 @@
           <t>DUPRAS Phenicia</t>
         </is>
       </c>
-      <c r="U150" t="inlineStr">
+      <c r="X150" t="inlineStr">
         <is>
           <t>56152</t>
         </is>
@@ -10632,7 +10747,7 @@
           <t>MUELLER Hannah</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr">
+      <c r="X151" t="inlineStr">
         <is>
           <t>63133</t>
         </is>
@@ -10695,7 +10810,7 @@
           <t>DOMAJNKO Helena</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr">
+      <c r="X152" t="inlineStr">
         <is>
           <t>83895</t>
         </is>
@@ -10758,7 +10873,7 @@
           <t>STEBLAJ Ana</t>
         </is>
       </c>
-      <c r="U153" t="inlineStr">
+      <c r="X153" t="inlineStr">
         <is>
           <t>94495</t>
         </is>
@@ -10821,7 +10936,7 @@
           <t>NEMCOVA Marie</t>
         </is>
       </c>
-      <c r="U154" t="inlineStr">
+      <c r="X154" t="inlineStr">
         <is>
           <t>78808</t>
         </is>
@@ -10884,7 +10999,7 @@
           <t>ROSA Mathilde Serena</t>
         </is>
       </c>
-      <c r="U155" t="inlineStr">
+      <c r="X155" t="inlineStr">
         <is>
           <t>39777</t>
         </is>
@@ -10947,7 +11062,7 @@
           <t>VINET Lise</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr">
+      <c r="X156" t="inlineStr">
         <is>
           <t>53291</t>
         </is>
@@ -11010,7 +11125,7 @@
           <t>PEREIRA MACHADO Luiz Antonio</t>
         </is>
       </c>
-      <c r="U157" t="inlineStr">
+      <c r="X157" t="inlineStr">
         <is>
           <t>113696</t>
         </is>
@@ -11073,7 +11188,7 @@
           <t>AVERSA Pedro</t>
         </is>
       </c>
-      <c r="U158" t="inlineStr">
+      <c r="X158" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
@@ -11136,7 +11251,7 @@
           <t>HOCEVAR Simeon</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr">
+      <c r="X159" t="inlineStr">
         <is>
           <t>36273</t>
         </is>
@@ -11199,7 +11314,7 @@
           <t>QUINTARELLI Federico</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
+      <c r="X160" t="inlineStr">
         <is>
           <t>75789</t>
         </is>
@@ -11262,7 +11377,7 @@
           <t>TOLIC Ivan</t>
         </is>
       </c>
-      <c r="U161" t="inlineStr">
+      <c r="X161" t="inlineStr">
         <is>
           <t>39671</t>
         </is>
@@ -11325,7 +11440,7 @@
           <t>ZONJIC Jadran</t>
         </is>
       </c>
-      <c r="U162" t="inlineStr">
+      <c r="X162" t="inlineStr">
         <is>
           <t>39640</t>
         </is>
@@ -11388,7 +11503,7 @@
           <t>GALE Martin</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr">
+      <c r="X163" t="inlineStr">
         <is>
           <t>93891</t>
         </is>
@@ -11451,7 +11566,7 @@
           <t>IVANECKY Jaromir</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr">
+      <c r="X164" t="inlineStr">
         <is>
           <t>98676</t>
         </is>
@@ -11514,7 +11629,7 @@
           <t>ZDRAVKOVIC Pavle</t>
         </is>
       </c>
-      <c r="U165" t="inlineStr">
+      <c r="X165" t="inlineStr">
         <is>
           <t>39964</t>
         </is>
@@ -11577,7 +11692,7 @@
           <t>GRADISEK Nejc</t>
         </is>
       </c>
-      <c r="U166" t="inlineStr">
+      <c r="X166" t="inlineStr">
         <is>
           <t>83918</t>
         </is>
@@ -11640,7 +11755,7 @@
           <t>SCHWARZ Ole</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr">
+      <c r="X167" t="inlineStr">
         <is>
           <t>76065</t>
         </is>
@@ -11703,7 +11818,7 @@
           <t>VANEK Matej</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr">
+      <c r="X168" t="inlineStr">
         <is>
           <t>98305</t>
         </is>
@@ -11766,7 +11881,7 @@
           <t>OBADIC Luka</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr">
+      <c r="X169" t="inlineStr">
         <is>
           <t>39639</t>
         </is>
@@ -11829,7 +11944,7 @@
           <t>HALES Antonin</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr">
+      <c r="X170" t="inlineStr">
         <is>
           <t>35515</t>
         </is>
@@ -11892,7 +12007,7 @@
           <t>MAPELLI Tommaso</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr">
+      <c r="X171" t="inlineStr">
         <is>
           <t>75795</t>
         </is>
@@ -11955,7 +12070,7 @@
           <t>SAUTEUR Nicolas</t>
         </is>
       </c>
-      <c r="U172" t="inlineStr">
+      <c r="X172" t="inlineStr">
         <is>
           <t>63173</t>
         </is>
@@ -12018,7 +12133,7 @@
           <t>QUINTARELLI Mattia</t>
         </is>
       </c>
-      <c r="U173" t="inlineStr">
+      <c r="X173" t="inlineStr">
         <is>
           <t>39775</t>
         </is>
@@ -12081,7 +12196,7 @@
           <t>BENUS Matej</t>
         </is>
       </c>
-      <c r="U174" t="inlineStr">
+      <c r="X174" t="inlineStr">
         <is>
           <t>35353</t>
         </is>
@@ -12144,7 +12259,7 @@
           <t>BIANCHETTI Giacomo</t>
         </is>
       </c>
-      <c r="U175" t="inlineStr">
+      <c r="X175" t="inlineStr">
         <is>
           <t>75796</t>
         </is>
@@ -12207,7 +12322,7 @@
           <t>DANIK Ladislav</t>
         </is>
       </c>
-      <c r="U176" t="inlineStr">
+      <c r="X176" t="inlineStr">
         <is>
           <t>82996</t>
         </is>
@@ -12270,7 +12385,7 @@
           <t>OLAR Matteo-Alexander</t>
         </is>
       </c>
-      <c r="U177" t="inlineStr">
+      <c r="X177" t="inlineStr">
         <is>
           <t>104625</t>
         </is>
@@ -12333,7 +12448,7 @@
           <t>FENTANES Ricardo</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr">
+      <c r="X178" t="inlineStr">
         <is>
           <t>94184</t>
         </is>
@@ -12396,7 +12511,7 @@
           <t>WEWEGE Donovan</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr">
+      <c r="X179" t="inlineStr">
         <is>
           <t>39241</t>
         </is>
@@ -12459,7 +12574,7 @@
           <t>MUTURI Samuel</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr">
+      <c r="X180" t="inlineStr">
         <is>
           <t>68743</t>
         </is>
@@ -12522,7 +12637,7 @@
           <t>ONG Jun Yi</t>
         </is>
       </c>
-      <c r="U181" t="inlineStr">
+      <c r="X181" t="inlineStr">
         <is>
           <t>75421</t>
         </is>
@@ -12585,7 +12700,7 @@
           <t>KOZMA Patrick</t>
         </is>
       </c>
-      <c r="U182" t="inlineStr">
+      <c r="X182" t="inlineStr">
         <is>
           <t>104624</t>
         </is>
@@ -12648,7 +12763,7 @@
           <t>PLAUDIS Martins</t>
         </is>
       </c>
-      <c r="U183" t="inlineStr">
+      <c r="X183" t="inlineStr">
         <is>
           <t>106153</t>
         </is>
@@ -12711,7 +12826,7 @@
           <t>BAKOVIC Ignacio</t>
         </is>
       </c>
-      <c r="U184" t="inlineStr">
+      <c r="X184" t="inlineStr">
         <is>
           <t>85146</t>
         </is>
@@ -12774,7 +12889,7 @@
           <t>BLODER Marcel</t>
         </is>
       </c>
-      <c r="U185" t="inlineStr">
+      <c r="X185" t="inlineStr">
         <is>
           <t>46839</t>
         </is>
@@ -12837,7 +12952,7 @@
           <t>DE PAULA Andre Luiz</t>
         </is>
       </c>
-      <c r="U186" t="inlineStr">
+      <c r="X186" t="inlineStr">
         <is>
           <t>93227</t>
         </is>
@@ -12900,7 +13015,7 @@
           <t>STROUSE Garet</t>
         </is>
       </c>
-      <c r="U187" t="inlineStr">
+      <c r="X187" t="inlineStr">
         <is>
           <t>104490</t>
         </is>
@@ -12963,7 +13078,7 @@
           <t>WINKLER Paul</t>
         </is>
       </c>
-      <c r="U188" t="inlineStr">
+      <c r="X188" t="inlineStr">
         <is>
           <t>105625</t>
         </is>
@@ -13026,7 +13141,7 @@
           <t>DIMITRIJEVIC Ognjen</t>
         </is>
       </c>
-      <c r="U189" t="inlineStr">
+      <c r="X189" t="inlineStr">
         <is>
           <t>39961</t>
         </is>
@@ -13089,7 +13204,7 @@
           <t>RAGHAVAN Kartik</t>
         </is>
       </c>
-      <c r="U190" t="inlineStr">
+      <c r="X190" t="inlineStr">
         <is>
           <t>96666</t>
         </is>
@@ -13152,7 +13267,7 @@
           <t>JEFFERIES Robert</t>
         </is>
       </c>
-      <c r="U191" t="inlineStr">
+      <c r="X191" t="inlineStr">
         <is>
           <t>53202</t>
         </is>
@@ -13215,7 +13330,7 @@
           <t>HOLMES Jacob</t>
         </is>
       </c>
-      <c r="U192" t="inlineStr">
+      <c r="X192" t="inlineStr">
         <is>
           <t>53139</t>
         </is>
@@ -13278,7 +13393,7 @@
           <t>KASTNER Eric</t>
         </is>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="X193" t="inlineStr">
         <is>
           <t>75626</t>
         </is>
@@ -13341,7 +13456,7 @@
           <t>BOLZERN Linus</t>
         </is>
       </c>
-      <c r="U194" t="inlineStr">
+      <c r="X194" t="inlineStr">
         <is>
           <t>56069</t>
         </is>
@@ -13404,7 +13519,7 @@
           <t>RAJNIAK Boris</t>
         </is>
       </c>
-      <c r="U195" t="inlineStr">
+      <c r="X195" t="inlineStr">
         <is>
           <t>37309</t>
         </is>
@@ -13467,7 +13582,7 @@
           <t>BARTHEL Bjoern</t>
         </is>
       </c>
-      <c r="U196" t="inlineStr">
+      <c r="X196" t="inlineStr">
         <is>
           <t>36675</t>
         </is>
@@ -13530,7 +13645,7 @@
           <t>TAHIROVIC Alen</t>
         </is>
       </c>
-      <c r="U197" t="inlineStr">
+      <c r="X197" t="inlineStr">
         <is>
           <t>87291</t>
         </is>
@@ -13593,7 +13708,7 @@
           <t>MARJANOVIC Marko</t>
         </is>
       </c>
-      <c r="U198" t="inlineStr">
+      <c r="X198" t="inlineStr">
         <is>
           <t>43084</t>
         </is>
@@ -13656,7 +13771,7 @@
           <t>HEBORT Samuel</t>
         </is>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="X199" t="inlineStr">
         <is>
           <t>96068</t>
         </is>
@@ -13719,7 +13834,7 @@
           <t>MONTULET Leo</t>
         </is>
       </c>
-      <c r="U200" t="inlineStr">
+      <c r="X200" t="inlineStr">
         <is>
           <t>70119</t>
         </is>
@@ -13782,7 +13897,7 @@
           <t>MACUS Ondrej</t>
         </is>
       </c>
-      <c r="U201" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>94095</t>
         </is>
@@ -13845,7 +13960,7 @@
           <t>BROWN Frederick</t>
         </is>
       </c>
-      <c r="U202" t="inlineStr">
+      <c r="X202" t="inlineStr">
         <is>
           <t>79368</t>
         </is>
@@ -13908,7 +14023,7 @@
           <t>ABBIATI Giacomo</t>
         </is>
       </c>
-      <c r="U203" t="inlineStr">
+      <c r="X203" t="inlineStr">
         <is>
           <t>94769</t>
         </is>
@@ -13971,7 +14086,7 @@
           <t>ZAPLETAL Mikulas</t>
         </is>
       </c>
-      <c r="U204" t="inlineStr">
+      <c r="X204" t="inlineStr">
         <is>
           <t>63523</t>
         </is>
@@ -14034,7 +14149,7 @@
           <t>PYPE Samuel</t>
         </is>
       </c>
-      <c r="U205" t="inlineStr">
+      <c r="X205" t="inlineStr">
         <is>
           <t>54038</t>
         </is>
@@ -14097,7 +14212,7 @@
           <t>KANISCAK Kamil</t>
         </is>
       </c>
-      <c r="U206" t="inlineStr">
+      <c r="X206" t="inlineStr">
         <is>
           <t>36674</t>
         </is>
@@ -14160,7 +14275,7 @@
           <t>URANKAR Anze</t>
         </is>
       </c>
-      <c r="U207" t="inlineStr">
+      <c r="X207" t="inlineStr">
         <is>
           <t>44341</t>
         </is>
@@ -14223,7 +14338,7 @@
           <t>SATKE Adam</t>
         </is>
       </c>
-      <c r="U208" t="inlineStr">
+      <c r="X208" t="inlineStr">
         <is>
           <t>70681</t>
         </is>
@@ -14286,7 +14401,7 @@
           <t>HAEFELI Robin</t>
         </is>
       </c>
-      <c r="U209" t="inlineStr">
+      <c r="X209" t="inlineStr">
         <is>
           <t>76130</t>
         </is>
@@ -14349,7 +14464,7 @@
           <t>OVEN Simon</t>
         </is>
       </c>
-      <c r="U210" t="inlineStr">
+      <c r="X210" t="inlineStr">
         <is>
           <t>38164</t>
         </is>
@@ -14412,7 +14527,7 @@
           <t>NOVAK Tim</t>
         </is>
       </c>
-      <c r="U211" t="inlineStr">
+      <c r="X211" t="inlineStr">
         <is>
           <t>55802</t>
         </is>
@@ -14475,7 +14590,7 @@
           <t>CIOTOLI Francesco</t>
         </is>
       </c>
-      <c r="U212" t="inlineStr">
+      <c r="X212" t="inlineStr">
         <is>
           <t>70132</t>
         </is>
@@ -14538,7 +14653,7 @@
           <t>FENGLER Till</t>
         </is>
       </c>
-      <c r="U213" t="inlineStr">
+      <c r="X213" t="inlineStr">
         <is>
           <t>95456</t>
         </is>
@@ -14601,7 +14716,7 @@
           <t>BEERSCHWENGER Bjoern</t>
         </is>
       </c>
-      <c r="U214" t="inlineStr">
+      <c r="X214" t="inlineStr">
         <is>
           <t>37662</t>
         </is>
@@ -14664,7 +14779,7 @@
           <t>BERNARDI Andrea</t>
         </is>
       </c>
-      <c r="U215" t="inlineStr">
+      <c r="X215" t="inlineStr">
         <is>
           <t>63276</t>
         </is>
@@ -14727,7 +14842,7 @@
           <t>ZNIDARCIC Nejc</t>
         </is>
       </c>
-      <c r="U216" t="inlineStr">
+      <c r="X216" t="inlineStr">
         <is>
           <t>37764</t>
         </is>
@@ -14790,7 +14905,7 @@
           <t>BARONE Luca</t>
         </is>
       </c>
-      <c r="U217" t="inlineStr">
+      <c r="X217" t="inlineStr">
         <is>
           <t>94780</t>
         </is>
@@ -14853,7 +14968,7 @@
           <t>SCHOLCZOVA Viktoria</t>
         </is>
       </c>
-      <c r="U218" t="inlineStr">
+      <c r="X218" t="inlineStr">
         <is>
           <t>89134</t>
         </is>
@@ -14916,7 +15031,7 @@
           <t>KNEBLOVA Tereza</t>
         </is>
       </c>
-      <c r="U219" t="inlineStr">
+      <c r="X219" t="inlineStr">
         <is>
           <t>83782</t>
         </is>
@@ -14979,7 +15094,7 @@
           <t>SATKOVA Martina</t>
         </is>
       </c>
-      <c r="U220" t="inlineStr">
+      <c r="X220" t="inlineStr">
         <is>
           <t>42008</t>
         </is>
@@ -15042,7 +15157,7 @@
           <t>BARM Sabrina</t>
         </is>
       </c>
-      <c r="U221" t="inlineStr">
+      <c r="X221" t="inlineStr">
         <is>
           <t>35175</t>
         </is>
@@ -15105,7 +15220,7 @@
           <t>DZIADKOVA Zuzana</t>
         </is>
       </c>
-      <c r="U222" t="inlineStr">
+      <c r="X222" t="inlineStr">
         <is>
           <t>98317</t>
         </is>
@@ -15168,7 +15283,7 @@
           <t>FONTAINE Laura</t>
         </is>
       </c>
-      <c r="U223" t="inlineStr">
+      <c r="X223" t="inlineStr">
         <is>
           <t>98758</t>
         </is>
@@ -15231,7 +15346,7 @@
           <t>GRZIN Alba Zoe</t>
         </is>
       </c>
-      <c r="U224" t="inlineStr">
+      <c r="X224" t="inlineStr">
         <is>
           <t>39677</t>
         </is>
@@ -15294,7 +15409,7 @@
           <t>KOPUNOVA Katarina</t>
         </is>
       </c>
-      <c r="U225" t="inlineStr">
+      <c r="X225" t="inlineStr">
         <is>
           <t>35471</t>
         </is>
@@ -15357,7 +15472,7 @@
           <t>NEMCOVA Marie</t>
         </is>
       </c>
-      <c r="U226" t="inlineStr">
+      <c r="X226" t="inlineStr">
         <is>
           <t>78808</t>
         </is>
@@ -15420,7 +15535,7 @@
           <t>RAGUENES Helene</t>
         </is>
       </c>
-      <c r="U227" t="inlineStr">
+      <c r="X227" t="inlineStr">
         <is>
           <t>76819</t>
         </is>
@@ -15483,7 +15598,7 @@
           <t>GAUBERT Elsa</t>
         </is>
       </c>
-      <c r="U228" t="inlineStr">
+      <c r="X228" t="inlineStr">
         <is>
           <t>76817</t>
         </is>
@@ -15546,7 +15661,7 @@
           <t>PANATO Cecilia</t>
         </is>
       </c>
-      <c r="U229" t="inlineStr">
+      <c r="X229" t="inlineStr">
         <is>
           <t>75522</t>
         </is>
@@ -15614,12 +15729,12 @@
           <t>NOVAK Martin</t>
         </is>
       </c>
-      <c r="U230" t="inlineStr">
+      <c r="X230" t="inlineStr">
         <is>
           <t>35515</t>
         </is>
       </c>
-      <c r="V230" t="inlineStr">
+      <c r="Y230" t="inlineStr">
         <is>
           <t>42247</t>
         </is>
@@ -15687,12 +15802,12 @@
           <t>DE PAULA Andre Luiz</t>
         </is>
       </c>
-      <c r="U231" t="inlineStr">
+      <c r="X231" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
       </c>
-      <c r="V231" t="inlineStr">
+      <c r="Y231" t="inlineStr">
         <is>
           <t>93227</t>
         </is>
@@ -15760,12 +15875,12 @@
           <t>GALE Martin</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
+      <c r="X232" t="inlineStr">
         <is>
           <t>83918</t>
         </is>
       </c>
-      <c r="V232" t="inlineStr">
+      <c r="Y232" t="inlineStr">
         <is>
           <t>93891</t>
         </is>
@@ -15833,12 +15948,12 @@
           <t>QUINTARELLI Mattia</t>
         </is>
       </c>
-      <c r="U233" t="inlineStr">
+      <c r="X233" t="inlineStr">
         <is>
           <t>75789</t>
         </is>
       </c>
-      <c r="V233" t="inlineStr">
+      <c r="Y233" t="inlineStr">
         <is>
           <t>39775</t>
         </is>
@@ -15906,12 +16021,12 @@
           <t>LIPPERHEIDE Moritz</t>
         </is>
       </c>
-      <c r="U234" t="inlineStr">
+      <c r="X234" t="inlineStr">
         <is>
           <t>76065</t>
         </is>
       </c>
-      <c r="V234" t="inlineStr">
+      <c r="Y234" t="inlineStr">
         <is>
           <t>112668</t>
         </is>
@@ -15979,12 +16094,12 @@
           <t>SRAMEK Michal</t>
         </is>
       </c>
-      <c r="U235" t="inlineStr">
+      <c r="X235" t="inlineStr">
         <is>
           <t>35505</t>
         </is>
       </c>
-      <c r="V235" t="inlineStr">
+      <c r="Y235" t="inlineStr">
         <is>
           <t>35504</t>
         </is>
@@ -16052,12 +16167,12 @@
           <t>ROLENC Ondrej</t>
         </is>
       </c>
-      <c r="U236" t="inlineStr">
+      <c r="X236" t="inlineStr">
         <is>
           <t>42246</t>
         </is>
       </c>
-      <c r="V236" t="inlineStr">
+      <c r="Y236" t="inlineStr">
         <is>
           <t>35512</t>
         </is>
@@ -16125,12 +16240,12 @@
           <t>HOCHSCHORNER Peter</t>
         </is>
       </c>
-      <c r="U237" t="inlineStr">
+      <c r="X237" t="inlineStr">
         <is>
           <t>35356</t>
         </is>
       </c>
-      <c r="V237" t="inlineStr">
+      <c r="Y237" t="inlineStr">
         <is>
           <t>35357</t>
         </is>
@@ -16198,12 +16313,12 @@
           <t>BIANCHETTI Giacomo</t>
         </is>
       </c>
-      <c r="U238" t="inlineStr">
+      <c r="X238" t="inlineStr">
         <is>
           <t>75795</t>
         </is>
       </c>
-      <c r="V238" t="inlineStr">
+      <c r="Y238" t="inlineStr">
         <is>
           <t>75796</t>
         </is>
@@ -16271,12 +16386,12 @@
           <t>MORET Hugues</t>
         </is>
       </c>
-      <c r="U239" t="inlineStr">
+      <c r="X239" t="inlineStr">
         <is>
           <t>39643</t>
         </is>
       </c>
-      <c r="V239" t="inlineStr">
+      <c r="Y239" t="inlineStr">
         <is>
           <t>56142</t>
         </is>
@@ -16344,12 +16459,12 @@
           <t>SAUTEUR Nicolas</t>
         </is>
       </c>
-      <c r="U240" t="inlineStr">
+      <c r="X240" t="inlineStr">
         <is>
           <t>56131</t>
         </is>
       </c>
-      <c r="V240" t="inlineStr">
+      <c r="Y240" t="inlineStr">
         <is>
           <t>63173</t>
         </is>
@@ -16417,12 +16532,12 @@
           <t>GEWISSLER Matus</t>
         </is>
       </c>
-      <c r="U241" t="inlineStr">
+      <c r="X241" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
       </c>
-      <c r="V241" t="inlineStr">
+      <c r="Y241" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
@@ -16490,12 +16605,12 @@
           <t>VESELY Petr</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
+      <c r="X242" t="inlineStr">
         <is>
           <t>53303</t>
         </is>
       </c>
-      <c r="V242" t="inlineStr">
+      <c r="Y242" t="inlineStr">
         <is>
           <t>35511</t>
         </is>
@@ -16563,12 +16678,12 @@
           <t>DAZEUR Quentin</t>
         </is>
       </c>
-      <c r="U243" t="inlineStr">
+      <c r="X243" t="inlineStr">
         <is>
           <t>36791</t>
         </is>
       </c>
-      <c r="V243" t="inlineStr">
+      <c r="Y243" t="inlineStr">
         <is>
           <t>43141</t>
         </is>
@@ -16636,12 +16751,12 @@
           <t>DE PAULA Andre Luiz</t>
         </is>
       </c>
-      <c r="U244" t="inlineStr">
+      <c r="X244" t="inlineStr">
         <is>
           <t>60498</t>
         </is>
       </c>
-      <c r="V244" t="inlineStr">
+      <c r="Y244" t="inlineStr">
         <is>
           <t>93227</t>
         </is>
@@ -16709,12 +16824,12 @@
           <t>BIANCHETTI Giacomo</t>
         </is>
       </c>
-      <c r="U245" t="inlineStr">
+      <c r="X245" t="inlineStr">
         <is>
           <t>75795</t>
         </is>
       </c>
-      <c r="V245" t="inlineStr">
+      <c r="Y245" t="inlineStr">
         <is>
           <t>75796</t>
         </is>
@@ -16782,12 +16897,12 @@
           <t>LIPPERHEIDE Moritz</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
+      <c r="X246" t="inlineStr">
         <is>
           <t>76065</t>
         </is>
       </c>
-      <c r="V246" t="inlineStr">
+      <c r="Y246" t="inlineStr">
         <is>
           <t>112668</t>
         </is>
@@ -16855,12 +16970,12 @@
           <t>GALE Martin</t>
         </is>
       </c>
-      <c r="U247" t="inlineStr">
+      <c r="X247" t="inlineStr">
         <is>
           <t>83918</t>
         </is>
       </c>
-      <c r="V247" t="inlineStr">
+      <c r="Y247" t="inlineStr">
         <is>
           <t>93891</t>
         </is>
@@ -16928,12 +17043,12 @@
           <t>GEWISSLER Matus</t>
         </is>
       </c>
-      <c r="U248" t="inlineStr">
+      <c r="X248" t="inlineStr">
         <is>
           <t>39248</t>
         </is>
       </c>
-      <c r="V248" t="inlineStr">
+      <c r="Y248" t="inlineStr">
         <is>
           <t>39249</t>
         </is>
@@ -17001,12 +17116,12 @@
           <t>SRAMEK Michal</t>
         </is>
       </c>
-      <c r="U249" t="inlineStr">
+      <c r="X249" t="inlineStr">
         <is>
           <t>35505</t>
         </is>
       </c>
-      <c r="V249" t="inlineStr">
+      <c r="Y249" t="inlineStr">
         <is>
           <t>35504</t>
         </is>
@@ -17074,12 +17189,12 @@
           <t>DAZEUR Quentin</t>
         </is>
       </c>
-      <c r="U250" t="inlineStr">
+      <c r="X250" t="inlineStr">
         <is>
           <t>36791</t>
         </is>
       </c>
-      <c r="V250" t="inlineStr">
+      <c r="Y250" t="inlineStr">
         <is>
           <t>43141</t>
         </is>
@@ -17147,12 +17262,12 @@
           <t>VESELY Petr</t>
         </is>
       </c>
-      <c r="U251" t="inlineStr">
+      <c r="X251" t="inlineStr">
         <is>
           <t>53303</t>
         </is>
       </c>
-      <c r="V251" t="inlineStr">
+      <c r="Y251" t="inlineStr">
         <is>
           <t>35511</t>
         </is>
@@ -17220,12 +17335,12 @@
           <t>SAUTEUR Nicolas</t>
         </is>
       </c>
-      <c r="U252" t="inlineStr">
+      <c r="X252" t="inlineStr">
         <is>
           <t>56131</t>
         </is>
       </c>
-      <c r="V252" t="inlineStr">
+      <c r="Y252" t="inlineStr">
         <is>
           <t>63173</t>
         </is>
@@ -17290,11 +17405,6 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>W</t>
-        </is>
-      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>SENIOR</t>
@@ -17312,7 +17422,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Heats</t>
+          <t>Forerunner</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -17327,30 +17437,20 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>08:32:30</t>
+          <t>13:32:00</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
         <is>
-          <t>CRO</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J254" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="K254" t="n">
         <v>253</v>
       </c>
-      <c r="R254" t="inlineStr">
-        <is>
-          <t>GRZIN Alba Zoe</t>
-        </is>
-      </c>
-      <c r="U254" t="inlineStr">
-        <is>
-          <t>39677</t>
-        </is>
-      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -17375,7 +17475,7 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Heats</t>
+          <t>Forerunner</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -17390,28 +17490,23 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>09:14:30</t>
+          <t>13:50:06</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J255" t="n">
-        <v>137</v>
+        <v>11</v>
       </c>
       <c r="K255" t="n">
         <v>254</v>
       </c>
       <c r="R255" t="inlineStr">
         <is>
-          <t>SOUDI Mathis</t>
-        </is>
-      </c>
-      <c r="U255" t="inlineStr">
-        <is>
-          <t>69447</t>
+          <t>MRUZEK Kamil</t>
         </is>
       </c>
     </row>
@@ -17438,12 +17533,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Heats</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -17453,35 +17548,45 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>09:47:00</t>
+          <t>14:00:06</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
         <is>
-          <t>NED</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J256" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="K256" t="n">
         <v>255</v>
       </c>
+      <c r="M256" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N256" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="R256" t="inlineStr">
         <is>
-          <t>WEGMAN Martina</t>
-        </is>
-      </c>
-      <c r="U256" t="inlineStr">
-        <is>
-          <t>35345</t>
+          <t>PANATO Cecilia</t>
+        </is>
+      </c>
+      <c r="X256" t="inlineStr">
+        <is>
+          <t>75522</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17491,7 +17596,7 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -17501,7 +17606,7 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Heats</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -17516,42 +17621,47 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>11:43:30</t>
+          <t>14:01:40</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
         <is>
-          <t>CRO</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="J257" t="n">
-        <v>4</v>
+        <v>66</v>
       </c>
       <c r="K257" t="n">
         <v>256</v>
       </c>
+      <c r="M257" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N257" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="R257" t="inlineStr">
         <is>
-          <t>OBADIC Luka</t>
-        </is>
-      </c>
-      <c r="S257" t="inlineStr">
-        <is>
-          <t>TOLIC Ivan</t>
-        </is>
-      </c>
-      <c r="U257" t="inlineStr">
-        <is>
-          <t>39639</t>
-        </is>
-      </c>
-      <c r="V257" t="inlineStr">
-        <is>
-          <t>39671</t>
+          <t>DREIER Valentina</t>
+        </is>
+      </c>
+      <c r="X257" t="inlineStr">
+        <is>
+          <t>41612</t>
         </is>
       </c>
     </row>
     <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>SENIOR</t>
@@ -17569,7 +17679,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Forerunner</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -17584,30 +17694,35 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>13:32:00</t>
+          <t>14:03:07</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J258" t="n">
-        <v>2</v>
+        <v>80</v>
       </c>
       <c r="K258" t="n">
         <v>257</v>
       </c>
       <c r="R258" t="inlineStr">
         <is>
-          <t>Forerunner 2</t>
+          <t>DOMAJNKO Helena</t>
+        </is>
+      </c>
+      <c r="X258" t="inlineStr">
+        <is>
+          <t>83895</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17627,7 +17742,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Forerunner</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -17642,23 +17757,38 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>13:50:06</t>
+          <t>14:04:36</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="J259" t="n">
-        <v>11</v>
+        <v>73</v>
       </c>
       <c r="K259" t="n">
         <v>258</v>
       </c>
+      <c r="M259" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N259" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R259" t="inlineStr">
         <is>
-          <t>MRUZEK Kamil</t>
+          <t>MILNE Laura</t>
+        </is>
+      </c>
+      <c r="X259" t="inlineStr">
+        <is>
+          <t>75768</t>
         </is>
       </c>
     </row>
@@ -17700,38 +17830,38 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>14:00:06</t>
+          <t>14:06:07</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J260" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="K260" t="n">
         <v>259</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R260" t="inlineStr">
         <is>
-          <t>PANATO Cecilia</t>
-        </is>
-      </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>75522</t>
+          <t>VALDENAIRE Mathilde</t>
+        </is>
+      </c>
+      <c r="X260" t="inlineStr">
+        <is>
+          <t>94782</t>
         </is>
       </c>
     </row>
@@ -17773,38 +17903,38 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>14:01:40</t>
+          <t>14:07:36</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J261" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K261" t="n">
         <v>260</v>
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R261" t="inlineStr">
         <is>
-          <t>DREIER Valentina</t>
-        </is>
-      </c>
-      <c r="U261" t="inlineStr">
-        <is>
-          <t>41612</t>
+          <t>STEBLAJ Ana</t>
+        </is>
+      </c>
+      <c r="X261" t="inlineStr">
+        <is>
+          <t>94495</t>
         </is>
       </c>
     </row>
@@ -17846,28 +17976,38 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>14:03:07</t>
+          <t>14:09:07</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J262" t="n">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="K262" t="n">
         <v>261</v>
       </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R262" t="inlineStr">
         <is>
-          <t>DOMAJNKO Helena</t>
-        </is>
-      </c>
-      <c r="U262" t="inlineStr">
-        <is>
-          <t>83895</t>
+          <t>VINET Lise</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>53291</t>
         </is>
       </c>
     </row>
@@ -17909,38 +18049,38 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>14:04:36</t>
+          <t>14:10:36</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="J263" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="K263" t="n">
         <v>262</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R263" t="inlineStr">
         <is>
-          <t>MILNE Laura</t>
-        </is>
-      </c>
-      <c r="U263" t="inlineStr">
-        <is>
-          <t>75768</t>
+          <t>MUELLER Hannah</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>63133</t>
         </is>
       </c>
     </row>
@@ -17982,38 +18122,38 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>14:06:07</t>
+          <t>14:12:08</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J264" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="K264" t="n">
         <v>263</v>
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R264" t="inlineStr">
         <is>
-          <t>VALDENAIRE Mathilde</t>
-        </is>
-      </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>94782</t>
+          <t>NEMCOVA Marie</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>78808</t>
         </is>
       </c>
     </row>
@@ -18055,38 +18195,38 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>14:07:36</t>
+          <t>14:13:39</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J265" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="K265" t="n">
         <v>264</v>
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>STEBLAJ Ana</t>
-        </is>
-      </c>
-      <c r="U265" t="inlineStr">
-        <is>
-          <t>94495</t>
+          <t>DUPRAS Phenicia</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>56152</t>
         </is>
       </c>
     </row>
@@ -18128,38 +18268,38 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>14:09:07</t>
+          <t>14:15:08</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J266" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K266" t="n">
         <v>265</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>VINET Lise</t>
-        </is>
-      </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>53291</t>
+          <t>ECKERT Jil-Sophie</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>39763</t>
         </is>
       </c>
     </row>
@@ -18201,38 +18341,38 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>14:10:36</t>
+          <t>14:16:36</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J267" t="n">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="K267" t="n">
         <v>266</v>
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R267" t="inlineStr">
         <is>
-          <t>MUELLER Hannah</t>
-        </is>
-      </c>
-      <c r="U267" t="inlineStr">
-        <is>
-          <t>63133</t>
+          <t>KNEBLOVA Tereza</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>83782</t>
         </is>
       </c>
     </row>
@@ -18274,38 +18414,38 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>14:12:08</t>
+          <t>14:18:08</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J268" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K268" t="n">
         <v>267</v>
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R268" t="inlineStr">
         <is>
-          <t>NEMCOVA Marie</t>
-        </is>
-      </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>78808</t>
+          <t>KOSTLE Elisabeth</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>64811</t>
         </is>
       </c>
     </row>
@@ -18347,7 +18487,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>14:13:39</t>
+          <t>14:19:38</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -18356,29 +18496,29 @@
         </is>
       </c>
       <c r="J269" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="K269" t="n">
         <v>268</v>
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R269" t="inlineStr">
         <is>
-          <t>DUPRAS Phenicia</t>
-        </is>
-      </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>56152</t>
+          <t>FRESLON Pauline</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>75974</t>
         </is>
       </c>
     </row>
@@ -18420,45 +18560,45 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>14:15:08</t>
+          <t>14:21:06</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J270" t="n">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="K270" t="n">
         <v>269</v>
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R270" t="inlineStr">
         <is>
-          <t>ECKERT Jil-Sophie</t>
-        </is>
-      </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>39763</t>
+          <t>SATKOVA Martina</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>42008</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -18468,7 +18608,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -18493,45 +18633,35 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>14:16:36</t>
+          <t>14:26:36</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J271" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="K271" t="n">
         <v>270</v>
       </c>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="N271" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="R271" t="inlineStr">
         <is>
-          <t>KNEBLOVA Tereza</t>
-        </is>
-      </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>83782</t>
+          <t>GALE Martin</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>93891</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -18541,7 +18671,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -18566,12 +18696,12 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>14:18:08</t>
+          <t>14:28:05</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J272" t="n">
@@ -18582,29 +18712,29 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R272" t="inlineStr">
         <is>
-          <t>KOSTLE Elisabeth</t>
-        </is>
-      </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>64811</t>
+          <t>DANIK Ladislav</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>82996</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -18614,7 +18744,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -18639,45 +18769,45 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>14:19:38</t>
+          <t>14:29:37</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J273" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K273" t="n">
         <v>272</v>
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R273" t="inlineStr">
         <is>
-          <t>FRESLON Pauline</t>
-        </is>
-      </c>
-      <c r="U273" t="inlineStr">
-        <is>
-          <t>75974</t>
+          <t>BIANCHETTI Giacomo</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>75796</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18687,7 +18817,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -18712,7 +18842,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>14:21:06</t>
+          <t>14:31:05</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -18721,29 +18851,29 @@
         </is>
       </c>
       <c r="J274" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K274" t="n">
         <v>273</v>
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R274" t="inlineStr">
         <is>
-          <t>SATKOVA Martina</t>
-        </is>
-      </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>42008</t>
+          <t>VANEK Matej</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>98305</t>
         </is>
       </c>
     </row>
@@ -18785,28 +18915,38 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>14:26:36</t>
+          <t>14:32:36</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J275" t="n">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="K275" t="n">
         <v>274</v>
       </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="R275" t="inlineStr">
         <is>
-          <t>GALE Martin</t>
-        </is>
-      </c>
-      <c r="U275" t="inlineStr">
-        <is>
-          <t>93891</t>
+          <t>QUINTARELLI Mattia</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>39775</t>
         </is>
       </c>
     </row>
@@ -18848,38 +18988,38 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>14:28:05</t>
+          <t>14:34:07</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J276" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="K276" t="n">
         <v>275</v>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R276" t="inlineStr">
         <is>
-          <t>DANIK Ladislav</t>
-        </is>
-      </c>
-      <c r="U276" t="inlineStr">
-        <is>
-          <t>82996</t>
+          <t>MAPELLI Tommaso</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>75795</t>
         </is>
       </c>
     </row>
@@ -18921,38 +19061,38 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>14:29:37</t>
+          <t>14:35:37</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J277" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="K277" t="n">
         <v>276</v>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R277" t="inlineStr">
         <is>
-          <t>BIANCHETTI Giacomo</t>
-        </is>
-      </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>75796</t>
+          <t>SAUTEUR Nicolas</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>63173</t>
         </is>
       </c>
     </row>
@@ -18994,38 +19134,38 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>14:31:05</t>
+          <t>14:37:05</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J278" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K278" t="n">
         <v>277</v>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R278" t="inlineStr">
         <is>
-          <t>VANEK Matej</t>
-        </is>
-      </c>
-      <c r="U278" t="inlineStr">
-        <is>
-          <t>98305</t>
+          <t>FERRION Charles</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>94783</t>
         </is>
       </c>
     </row>
@@ -19067,38 +19207,38 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>14:32:36</t>
+          <t>14:38:35</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J279" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="K279" t="n">
         <v>278</v>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R279" t="inlineStr">
         <is>
-          <t>QUINTARELLI Mattia</t>
-        </is>
-      </c>
-      <c r="U279" t="inlineStr">
-        <is>
-          <t>39775</t>
+          <t>DAZEUR Quentin</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>43141</t>
         </is>
       </c>
     </row>
@@ -19140,38 +19280,38 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>14:34:07</t>
+          <t>14:40:05</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J280" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="K280" t="n">
         <v>279</v>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R280" t="inlineStr">
         <is>
-          <t>MAPELLI Tommaso</t>
-        </is>
-      </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>75795</t>
+          <t>ROLENC Ondrej</t>
+        </is>
+      </c>
+      <c r="X280" t="inlineStr">
+        <is>
+          <t>35512</t>
         </is>
       </c>
     </row>
@@ -19213,38 +19353,38 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>14:35:37</t>
+          <t>14:41:36</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J281" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K281" t="n">
         <v>280</v>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R281" t="inlineStr">
         <is>
-          <t>SAUTEUR Nicolas</t>
-        </is>
-      </c>
-      <c r="U281" t="inlineStr">
-        <is>
-          <t>63173</t>
+          <t>SLANINA Vladimir</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>35516</t>
         </is>
       </c>
     </row>
@@ -19286,7 +19426,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>14:37:05</t>
+          <t>14:43:07</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -19295,29 +19435,29 @@
         </is>
       </c>
       <c r="J282" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K282" t="n">
         <v>281</v>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R282" t="inlineStr">
         <is>
-          <t>FERRION Charles</t>
-        </is>
-      </c>
-      <c r="U282" t="inlineStr">
-        <is>
-          <t>94783</t>
+          <t>KLATT Etienne</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>56165</t>
         </is>
       </c>
     </row>
@@ -19334,7 +19474,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
@@ -19359,45 +19499,45 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>14:38:35</t>
+          <t>14:48:35</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J283" t="n">
-        <v>62</v>
+        <v>118</v>
       </c>
       <c r="K283" t="n">
         <v>282</v>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R283" t="inlineStr">
         <is>
-          <t>DAZEUR Quentin</t>
-        </is>
-      </c>
-      <c r="U283" t="inlineStr">
-        <is>
-          <t>43141</t>
+          <t>BEERSCHWENGER Bjoern</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>37662</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -19407,7 +19547,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -19417,7 +19557,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Teams</t>
+          <t>Final</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -19432,48 +19572,38 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>14:39:00</t>
+          <t>14:50:07</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J284" t="n">
-        <v>12</v>
+        <v>122</v>
       </c>
       <c r="K284" t="n">
         <v>283</v>
       </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="R284" t="inlineStr">
         <is>
-          <t>KNEBLOVA Tereza</t>
-        </is>
-      </c>
-      <c r="S284" t="inlineStr">
-        <is>
-          <t>DZIADKOVA Zuzana</t>
-        </is>
-      </c>
-      <c r="T284" t="inlineStr">
-        <is>
-          <t>NEMCOVA Marie</t>
-        </is>
-      </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>83782</t>
-        </is>
-      </c>
-      <c r="V284" t="inlineStr">
-        <is>
-          <t>98317</t>
-        </is>
-      </c>
-      <c r="W284" t="inlineStr">
-        <is>
-          <t>78808</t>
+          <t>FENGLER Till</t>
+        </is>
+      </c>
+      <c r="X284" t="inlineStr">
+        <is>
+          <t>95456</t>
         </is>
       </c>
     </row>
@@ -19490,7 +19620,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -19515,38 +19645,38 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>14:40:05</t>
+          <t>14:51:36</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J285" t="n">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="K285" t="n">
         <v>284</v>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R285" t="inlineStr">
         <is>
-          <t>ROLENC Ondrej</t>
-        </is>
-      </c>
-      <c r="U285" t="inlineStr">
-        <is>
-          <t>35512</t>
+          <t>NOVAK Tim</t>
+        </is>
+      </c>
+      <c r="X285" t="inlineStr">
+        <is>
+          <t>55802</t>
         </is>
       </c>
     </row>
@@ -19563,7 +19693,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -19588,7 +19718,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>14:41:36</t>
+          <t>14:53:04</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -19597,29 +19727,29 @@
         </is>
       </c>
       <c r="J286" t="n">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="K286" t="n">
         <v>285</v>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R286" t="inlineStr">
         <is>
-          <t>SLANINA Vladimir</t>
-        </is>
-      </c>
-      <c r="U286" t="inlineStr">
-        <is>
-          <t>35516</t>
+          <t>SATKE Adam</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>70681</t>
         </is>
       </c>
     </row>
@@ -19636,7 +19766,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -19661,38 +19791,38 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>14:43:07</t>
+          <t>14:54:35</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J287" t="n">
-        <v>65</v>
+        <v>111</v>
       </c>
       <c r="K287" t="n">
         <v>286</v>
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R287" t="inlineStr">
         <is>
-          <t>KLATT Etienne</t>
-        </is>
-      </c>
-      <c r="U287" t="inlineStr">
-        <is>
-          <t>56165</t>
+          <t>BERNARDI Andrea</t>
+        </is>
+      </c>
+      <c r="X287" t="inlineStr">
+        <is>
+          <t>63276</t>
         </is>
       </c>
     </row>
@@ -19734,38 +19864,38 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>14:48:35</t>
+          <t>14:56:05</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>SUI</t>
         </is>
       </c>
       <c r="J288" t="n">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="K288" t="n">
         <v>287</v>
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R288" t="inlineStr">
         <is>
-          <t>BEERSCHWENGER Bjoern</t>
-        </is>
-      </c>
-      <c r="U288" t="inlineStr">
-        <is>
-          <t>37662</t>
+          <t>BOLZERN Linus</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>56069</t>
         </is>
       </c>
     </row>
@@ -19807,38 +19937,38 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>14:50:07</t>
+          <t>14:57:35</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J289" t="n">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K289" t="n">
         <v>288</v>
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="R289" t="inlineStr">
         <is>
-          <t>FENGLER Till</t>
-        </is>
-      </c>
-      <c r="U289" t="inlineStr">
-        <is>
-          <t>95456</t>
+          <t>ZAPLETAL Mikulas</t>
+        </is>
+      </c>
+      <c r="X289" t="inlineStr">
+        <is>
+          <t>63523</t>
         </is>
       </c>
     </row>
@@ -19880,38 +20010,38 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>14:51:36</t>
+          <t>14:59:10</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J290" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="K290" t="n">
         <v>289</v>
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R290" t="inlineStr">
         <is>
-          <t>NOVAK Tim</t>
-        </is>
-      </c>
-      <c r="U290" t="inlineStr">
-        <is>
-          <t>55802</t>
+          <t>BARONE Luca</t>
+        </is>
+      </c>
+      <c r="X290" t="inlineStr">
+        <is>
+          <t>94780</t>
         </is>
       </c>
     </row>
@@ -19953,38 +20083,38 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>14:53:04</t>
+          <t>15:00:34</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J291" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K291" t="n">
         <v>290</v>
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R291" t="inlineStr">
         <is>
-          <t>SATKE Adam</t>
-        </is>
-      </c>
-      <c r="U291" t="inlineStr">
-        <is>
-          <t>70681</t>
+          <t>URANKAR Anze</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>44341</t>
         </is>
       </c>
     </row>
@@ -20026,38 +20156,38 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>14:54:35</t>
+          <t>15:02:06</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J292" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="K292" t="n">
         <v>291</v>
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R292" t="inlineStr">
         <is>
-          <t>BERNARDI Andrea</t>
-        </is>
-      </c>
-      <c r="U292" t="inlineStr">
-        <is>
-          <t>63276</t>
+          <t>ZNIDARCIC Nejc</t>
+        </is>
+      </c>
+      <c r="X292" t="inlineStr">
+        <is>
+          <t>37764</t>
         </is>
       </c>
     </row>
@@ -20099,38 +20229,38 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>14:56:05</t>
+          <t>15:03:37</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>SUI</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J293" t="n">
-        <v>126</v>
+        <v>104</v>
       </c>
       <c r="K293" t="n">
         <v>292</v>
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R293" t="inlineStr">
         <is>
-          <t>BOLZERN Linus</t>
-        </is>
-      </c>
-      <c r="U293" t="inlineStr">
-        <is>
-          <t>56069</t>
+          <t>MORET Hugues</t>
+        </is>
+      </c>
+      <c r="X293" t="inlineStr">
+        <is>
+          <t>56142</t>
         </is>
       </c>
     </row>
@@ -20172,7 +20302,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>14:57:35</t>
+          <t>15:05:06</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -20181,29 +20311,29 @@
         </is>
       </c>
       <c r="J294" t="n">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="K294" t="n">
         <v>293</v>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R294" t="inlineStr">
         <is>
-          <t>ZAPLETAL Mikulas</t>
-        </is>
-      </c>
-      <c r="U294" t="inlineStr">
-        <is>
-          <t>63523</t>
+          <t>MATEJICEK Vojtech</t>
+        </is>
+      </c>
+      <c r="X294" t="inlineStr">
+        <is>
+          <t>87966</t>
         </is>
       </c>
     </row>
@@ -20245,7 +20375,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>14:59:10</t>
+          <t>15:06:35</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -20254,29 +20384,29 @@
         </is>
       </c>
       <c r="J295" t="n">
-        <v>120</v>
+        <v>102</v>
       </c>
       <c r="K295" t="n">
         <v>294</v>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R295" t="inlineStr">
         <is>
-          <t>BARONE Luca</t>
-        </is>
-      </c>
-      <c r="U295" t="inlineStr">
-        <is>
-          <t>94780</t>
+          <t>BAROUH Maxence</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>45024</t>
         </is>
       </c>
     </row>
@@ -20318,38 +20448,38 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>15:00:34</t>
+          <t>15:08:05</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J296" t="n">
-        <v>103</v>
+        <v>127</v>
       </c>
       <c r="K296" t="n">
         <v>295</v>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R296" t="inlineStr">
         <is>
-          <t>URANKAR Anze</t>
-        </is>
-      </c>
-      <c r="U296" t="inlineStr">
-        <is>
-          <t>44341</t>
+          <t>ZAPLETAL Vojtech</t>
+        </is>
+      </c>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>43285</t>
         </is>
       </c>
     </row>
@@ -20391,45 +20521,45 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>15:02:06</t>
+          <t>15:09:36</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J297" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="K297" t="n">
         <v>296</v>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R297" t="inlineStr">
         <is>
-          <t>ZNIDARCIC Nejc</t>
-        </is>
-      </c>
-      <c r="U297" t="inlineStr">
-        <is>
-          <t>37764</t>
+          <t>LEMMEN Yannic</t>
+        </is>
+      </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>45115</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -20439,7 +20569,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -20464,45 +20594,35 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>15:03:37</t>
+          <t>15:15:08</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CRO</t>
         </is>
       </c>
       <c r="J298" t="n">
-        <v>104</v>
+        <v>56</v>
       </c>
       <c r="K298" t="n">
         <v>297</v>
       </c>
-      <c r="M298" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="N298" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="R298" t="inlineStr">
         <is>
-          <t>MORET Hugues</t>
-        </is>
-      </c>
-      <c r="U298" t="inlineStr">
-        <is>
-          <t>56142</t>
+          <t>GRZIN Alba Zoe</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>39677</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -20512,7 +20632,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -20537,45 +20657,45 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>15:05:06</t>
+          <t>15:16:40</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>GER</t>
         </is>
       </c>
       <c r="J299" t="n">
-        <v>112</v>
+        <v>59</v>
       </c>
       <c r="K299" t="n">
         <v>298</v>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R299" t="inlineStr">
         <is>
-          <t>MATEJICEK Vojtech</t>
-        </is>
-      </c>
-      <c r="U299" t="inlineStr">
-        <is>
-          <t>87966</t>
+          <t>BARM Sabrina</t>
+        </is>
+      </c>
+      <c r="X299" t="inlineStr">
+        <is>
+          <t>35175</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -20585,7 +20705,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -20610,45 +20730,45 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>15:06:35</t>
+          <t>15:18:08</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J300" t="n">
-        <v>102</v>
+        <v>62</v>
       </c>
       <c r="K300" t="n">
         <v>299</v>
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="R300" t="inlineStr">
         <is>
-          <t>BAROUH Maxence</t>
-        </is>
-      </c>
-      <c r="U300" t="inlineStr">
-        <is>
-          <t>45024</t>
+          <t>SCHOLCZOVA Viktoria</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>89134</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -20658,7 +20778,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -20683,7 +20803,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>15:08:05</t>
+          <t>15:19:37</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -20692,36 +20812,36 @@
         </is>
       </c>
       <c r="J301" t="n">
-        <v>127</v>
+        <v>58</v>
       </c>
       <c r="K301" t="n">
         <v>300</v>
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R301" t="inlineStr">
         <is>
-          <t>ZAPLETAL Vojtech</t>
-        </is>
-      </c>
-      <c r="U301" t="inlineStr">
-        <is>
-          <t>43285</t>
+          <t>DZIADKOVA Zuzana</t>
+        </is>
+      </c>
+      <c r="X301" t="inlineStr">
+        <is>
+          <t>98317</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>W</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -20731,7 +20851,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -20756,38 +20876,38 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>15:09:36</t>
+          <t>15:21:07</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J302" t="n">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="K302" t="n">
         <v>301</v>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R302" t="inlineStr">
         <is>
-          <t>LEMMEN Yannic</t>
-        </is>
-      </c>
-      <c r="U302" t="inlineStr">
-        <is>
-          <t>45115</t>
+          <t>KOPUNOVA Katarina</t>
+        </is>
+      </c>
+      <c r="X302" t="inlineStr">
+        <is>
+          <t>35471</t>
         </is>
       </c>
     </row>
@@ -20829,28 +20949,38 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>15:15:08</t>
+          <t>15:22:37</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t>CRO</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J303" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K303" t="n">
         <v>302</v>
       </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R303" t="inlineStr">
         <is>
-          <t>GRZIN Alba Zoe</t>
-        </is>
-      </c>
-      <c r="U303" t="inlineStr">
-        <is>
-          <t>39677</t>
+          <t>SATKOVA Martina</t>
+        </is>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>42008</t>
         </is>
       </c>
     </row>
@@ -20892,38 +21022,38 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>15:16:40</t>
+          <t>15:24:11</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t>GER</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J304" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K304" t="n">
         <v>303</v>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R304" t="inlineStr">
         <is>
-          <t>BARM Sabrina</t>
-        </is>
-      </c>
-      <c r="U304" t="inlineStr">
-        <is>
-          <t>35175</t>
+          <t>FONTAINE Laura</t>
+        </is>
+      </c>
+      <c r="X304" t="inlineStr">
+        <is>
+          <t>98758</t>
         </is>
       </c>
     </row>
@@ -20965,38 +21095,38 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>15:18:08</t>
+          <t>15:25:40</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J305" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="K305" t="n">
         <v>304</v>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R305" t="inlineStr">
         <is>
-          <t>SCHOLCZOVA Viktoria</t>
-        </is>
-      </c>
-      <c r="U305" t="inlineStr">
-        <is>
-          <t>89134</t>
+          <t>RAGUENES Helene</t>
+        </is>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>76819</t>
         </is>
       </c>
     </row>
@@ -21038,38 +21168,38 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>15:19:37</t>
+          <t>15:27:10</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J306" t="n">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="K306" t="n">
         <v>305</v>
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R306" t="inlineStr">
         <is>
-          <t>DZIADKOVA Zuzana</t>
-        </is>
-      </c>
-      <c r="U306" t="inlineStr">
-        <is>
-          <t>98317</t>
+          <t>GAUBERT Elsa</t>
+        </is>
+      </c>
+      <c r="X306" t="inlineStr">
+        <is>
+          <t>76817</t>
         </is>
       </c>
     </row>
@@ -21111,38 +21241,38 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>15:21:07</t>
+          <t>15:28:37</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J307" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="K307" t="n">
         <v>306</v>
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R307" t="inlineStr">
         <is>
-          <t>KOPUNOVA Katarina</t>
-        </is>
-      </c>
-      <c r="U307" t="inlineStr">
-        <is>
-          <t>35471</t>
+          <t>PANATO Cecilia</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>75522</t>
         </is>
       </c>
     </row>
@@ -21184,7 +21314,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>15:22:37</t>
+          <t>15:30:07</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -21193,29 +21323,29 @@
         </is>
       </c>
       <c r="J308" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K308" t="n">
         <v>307</v>
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="R308" t="inlineStr">
         <is>
-          <t>SATKOVA Martina</t>
-        </is>
-      </c>
-      <c r="U308" t="inlineStr">
-        <is>
-          <t>42008</t>
+          <t>KNEBLOVA Tereza</t>
+        </is>
+      </c>
+      <c r="X308" t="inlineStr">
+        <is>
+          <t>83782</t>
         </is>
       </c>
     </row>
@@ -21257,45 +21387,45 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>15:24:11</t>
+          <t>15:31:39</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J309" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K309" t="n">
         <v>308</v>
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R309" t="inlineStr">
         <is>
-          <t>FONTAINE Laura</t>
-        </is>
-      </c>
-      <c r="U309" t="inlineStr">
-        <is>
-          <t>98758</t>
+          <t>NEMCOVA Marie</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>78808</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -21305,7 +21435,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -21330,7 +21460,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>15:25:40</t>
+          <t>15:37:05</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -21339,36 +21469,46 @@
         </is>
       </c>
       <c r="J310" t="n">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="K310" t="n">
         <v>309</v>
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="R310" t="inlineStr">
         <is>
-          <t>RAGUENES Helene</t>
-        </is>
-      </c>
-      <c r="U310" t="inlineStr">
-        <is>
-          <t>76819</t>
+          <t>GOURJAULT Ancelin</t>
+        </is>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>SAUTEUR Nicolas</t>
+        </is>
+      </c>
+      <c r="X310" t="inlineStr">
+        <is>
+          <t>56131</t>
+        </is>
+      </c>
+      <c r="Y310" t="inlineStr">
+        <is>
+          <t>63173</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -21378,7 +21518,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -21403,45 +21543,55 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>15:27:10</t>
+          <t>15:38:36</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="J311" t="n">
-        <v>52</v>
+        <v>10</v>
       </c>
       <c r="K311" t="n">
         <v>310</v>
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R311" t="inlineStr">
         <is>
-          <t>GAUBERT Elsa</t>
-        </is>
-      </c>
-      <c r="U311" t="inlineStr">
-        <is>
-          <t>76817</t>
+          <t>TOMEK Lukas</t>
+        </is>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>SRAMEK Michal</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>35505</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>35504</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -21451,7 +21601,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -21476,45 +21626,55 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>15:28:37</t>
+          <t>15:40:06</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SLO</t>
         </is>
       </c>
       <c r="J312" t="n">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="K312" t="n">
         <v>311</v>
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="R312" t="inlineStr">
         <is>
-          <t>PANATO Cecilia</t>
-        </is>
-      </c>
-      <c r="U312" t="inlineStr">
-        <is>
-          <t>75522</t>
+          <t>GRADISEK Nejc</t>
+        </is>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>GALE Martin</t>
+        </is>
+      </c>
+      <c r="X312" t="inlineStr">
+        <is>
+          <t>83918</t>
+        </is>
+      </c>
+      <c r="Y312" t="inlineStr">
+        <is>
+          <t>93891</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -21524,7 +21684,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -21549,16 +21709,16 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>15:30:07</t>
+          <t>15:41:35</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="J313" t="n">
-        <v>61</v>
+        <v>1</v>
       </c>
       <c r="K313" t="n">
         <v>312</v>
@@ -21575,19 +21735,29 @@
       </c>
       <c r="R313" t="inlineStr">
         <is>
-          <t>KNEBLOVA Tereza</t>
-        </is>
-      </c>
-      <c r="U313" t="inlineStr">
-        <is>
-          <t>83782</t>
+          <t>SANTAMARIA Stephane</t>
+        </is>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>DAZEUR Quentin</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>36791</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>43141</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -21597,7 +21767,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -21622,7 +21792,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>15:31:39</t>
+          <t>15:43:05</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -21631,7 +21801,7 @@
         </is>
       </c>
       <c r="J314" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="K314" t="n">
         <v>313</v>
@@ -21648,12 +21818,22 @@
       </c>
       <c r="R314" t="inlineStr">
         <is>
-          <t>NEMCOVA Marie</t>
-        </is>
-      </c>
-      <c r="U314" t="inlineStr">
-        <is>
-          <t>78808</t>
+          <t>RYGEL Marek</t>
+        </is>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>VESELY Petr</t>
+        </is>
+      </c>
+      <c r="X314" t="inlineStr">
+        <is>
+          <t>53303</t>
+        </is>
+      </c>
+      <c r="Y314" t="inlineStr">
+        <is>
+          <t>35511</t>
         </is>
       </c>
     </row>
@@ -21695,48 +21875,48 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>15:37:05</t>
+          <t>15:44:36</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="J315" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K315" t="n">
         <v>314</v>
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R315" t="inlineStr">
         <is>
-          <t>GOURJAULT Ancelin</t>
+          <t>QUINTARELLI Federico</t>
         </is>
       </c>
       <c r="S315" t="inlineStr">
         <is>
-          <t>SAUTEUR Nicolas</t>
-        </is>
-      </c>
-      <c r="U315" t="inlineStr">
-        <is>
-          <t>56131</t>
-        </is>
-      </c>
-      <c r="V315" t="inlineStr">
-        <is>
-          <t>63173</t>
+          <t>QUINTARELLI Mattia</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>75789</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>39775</t>
         </is>
       </c>
     </row>
@@ -21778,7 +21958,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>15:38:36</t>
+          <t>15:46:07</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -21787,39 +21967,39 @@
         </is>
       </c>
       <c r="J316" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K316" t="n">
         <v>315</v>
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R316" t="inlineStr">
         <is>
-          <t>TOMEK Lukas</t>
+          <t>HALES Antonin</t>
         </is>
       </c>
       <c r="S316" t="inlineStr">
         <is>
-          <t>SRAMEK Michal</t>
-        </is>
-      </c>
-      <c r="U316" t="inlineStr">
-        <is>
-          <t>35505</t>
-        </is>
-      </c>
-      <c r="V316" t="inlineStr">
-        <is>
-          <t>35504</t>
+          <t>NOVAK Martin</t>
+        </is>
+      </c>
+      <c r="X316" t="inlineStr">
+        <is>
+          <t>35515</t>
+        </is>
+      </c>
+      <c r="Y316" t="inlineStr">
+        <is>
+          <t>42247</t>
         </is>
       </c>
     </row>
@@ -21861,48 +22041,48 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>15:40:06</t>
+          <t>15:47:36</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t>SLO</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="J317" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="K317" t="n">
         <v>316</v>
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="R317" t="inlineStr">
         <is>
-          <t>GRADISEK Nejc</t>
+          <t>HOCHSCHORNER Pavol</t>
         </is>
       </c>
       <c r="S317" t="inlineStr">
         <is>
-          <t>GALE Martin</t>
-        </is>
-      </c>
-      <c r="U317" t="inlineStr">
-        <is>
-          <t>83918</t>
-        </is>
-      </c>
-      <c r="V317" t="inlineStr">
-        <is>
-          <t>93891</t>
+          <t>HOCHSCHORNER Peter</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>35356</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>35357</t>
         </is>
       </c>
     </row>
@@ -21944,7 +22124,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>15:41:35</t>
+          <t>15:49:10</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -21953,39 +22133,39 @@
         </is>
       </c>
       <c r="J318" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K318" t="n">
         <v>317</v>
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R318" t="inlineStr">
         <is>
-          <t>SANTAMARIA Stephane</t>
+          <t>TROUBADY Pierre</t>
         </is>
       </c>
       <c r="S318" t="inlineStr">
         <is>
-          <t>DAZEUR Quentin</t>
-        </is>
-      </c>
-      <c r="U318" t="inlineStr">
-        <is>
-          <t>36791</t>
-        </is>
-      </c>
-      <c r="V318" t="inlineStr">
-        <is>
-          <t>43141</t>
+          <t>MORET Hugues</t>
+        </is>
+      </c>
+      <c r="X318" t="inlineStr">
+        <is>
+          <t>39643</t>
+        </is>
+      </c>
+      <c r="Y318" t="inlineStr">
+        <is>
+          <t>56142</t>
         </is>
       </c>
     </row>
@@ -22027,7 +22207,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>15:43:05</t>
+          <t>15:50:37</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -22036,452 +22216,37 @@
         </is>
       </c>
       <c r="J319" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="K319" t="n">
         <v>318</v>
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R319" t="inlineStr">
         <is>
-          <t>RYGEL Marek</t>
+          <t>SUCHANEK Daniel</t>
         </is>
       </c>
       <c r="S319" t="inlineStr">
         <is>
-          <t>VESELY Petr</t>
-        </is>
-      </c>
-      <c r="U319" t="inlineStr">
-        <is>
-          <t>53303</t>
-        </is>
-      </c>
-      <c r="V319" t="inlineStr">
-        <is>
-          <t>35511</t>
-        </is>
-      </c>
-    </row>
-    <row r="320">
-      <c r="A320" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B320" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C320" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D320" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="E320" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F320" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G320" t="inlineStr">
-        <is>
-          <t>2021-09-25</t>
-        </is>
-      </c>
-      <c r="H320" t="inlineStr">
-        <is>
-          <t>15:44:36</t>
-        </is>
-      </c>
-      <c r="I320" t="inlineStr">
-        <is>
-          <t>ITA</t>
-        </is>
-      </c>
-      <c r="J320" t="n">
-        <v>12</v>
-      </c>
-      <c r="K320" t="n">
-        <v>319</v>
-      </c>
-      <c r="M320" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="N320" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R320" t="inlineStr">
-        <is>
-          <t>QUINTARELLI Federico</t>
-        </is>
-      </c>
-      <c r="S320" t="inlineStr">
-        <is>
-          <t>QUINTARELLI Mattia</t>
-        </is>
-      </c>
-      <c r="U320" t="inlineStr">
-        <is>
-          <t>75789</t>
-        </is>
-      </c>
-      <c r="V320" t="inlineStr">
-        <is>
-          <t>39775</t>
-        </is>
-      </c>
-    </row>
-    <row r="321">
-      <c r="A321" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B321" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C321" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D321" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="E321" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F321" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G321" t="inlineStr">
-        <is>
-          <t>2021-09-25</t>
-        </is>
-      </c>
-      <c r="H321" t="inlineStr">
-        <is>
-          <t>15:46:07</t>
-        </is>
-      </c>
-      <c r="I321" t="inlineStr">
-        <is>
-          <t>CZE</t>
-        </is>
-      </c>
-      <c r="J321" t="n">
-        <v>15</v>
-      </c>
-      <c r="K321" t="n">
-        <v>320</v>
-      </c>
-      <c r="M321" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="N321" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R321" t="inlineStr">
-        <is>
-          <t>HALES Antonin</t>
-        </is>
-      </c>
-      <c r="S321" t="inlineStr">
-        <is>
-          <t>NOVAK Martin</t>
-        </is>
-      </c>
-      <c r="U321" t="inlineStr">
-        <is>
-          <t>35515</t>
-        </is>
-      </c>
-      <c r="V321" t="inlineStr">
-        <is>
-          <t>42247</t>
-        </is>
-      </c>
-    </row>
-    <row r="322">
-      <c r="A322" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B322" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C322" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D322" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="E322" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F322" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>2021-09-25</t>
-        </is>
-      </c>
-      <c r="H322" t="inlineStr">
-        <is>
-          <t>15:47:36</t>
-        </is>
-      </c>
-      <c r="I322" t="inlineStr">
-        <is>
-          <t>SVK</t>
-        </is>
-      </c>
-      <c r="J322" t="n">
-        <v>8</v>
-      </c>
-      <c r="K322" t="n">
-        <v>321</v>
-      </c>
-      <c r="M322" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="N322" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R322" t="inlineStr">
-        <is>
-          <t>HOCHSCHORNER Pavol</t>
-        </is>
-      </c>
-      <c r="S322" t="inlineStr">
-        <is>
-          <t>HOCHSCHORNER Peter</t>
-        </is>
-      </c>
-      <c r="U322" t="inlineStr">
-        <is>
-          <t>35356</t>
-        </is>
-      </c>
-      <c r="V322" t="inlineStr">
-        <is>
-          <t>35357</t>
-        </is>
-      </c>
-    </row>
-    <row r="323">
-      <c r="A323" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B323" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C323" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D323" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="E323" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F323" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G323" t="inlineStr">
-        <is>
-          <t>2021-09-25</t>
-        </is>
-      </c>
-      <c r="H323" t="inlineStr">
-        <is>
-          <t>15:49:10</t>
-        </is>
-      </c>
-      <c r="I323" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="J323" t="n">
-        <v>6</v>
-      </c>
-      <c r="K323" t="n">
-        <v>322</v>
-      </c>
-      <c r="M323" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="N323" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R323" t="inlineStr">
-        <is>
-          <t>TROUBADY Pierre</t>
-        </is>
-      </c>
-      <c r="S323" t="inlineStr">
-        <is>
-          <t>MORET Hugues</t>
-        </is>
-      </c>
-      <c r="U323" t="inlineStr">
-        <is>
-          <t>39643</t>
-        </is>
-      </c>
-      <c r="V323" t="inlineStr">
-        <is>
-          <t>56142</t>
-        </is>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="B324" t="inlineStr">
-        <is>
-          <t>SENIOR</t>
-        </is>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>C2</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="E324" t="inlineStr">
-        <is>
-          <t>Final</t>
-        </is>
-      </c>
-      <c r="F324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G324" t="inlineStr">
-        <is>
-          <t>2021-09-25</t>
-        </is>
-      </c>
-      <c r="H324" t="inlineStr">
-        <is>
-          <t>15:50:37</t>
-        </is>
-      </c>
-      <c r="I324" t="inlineStr">
-        <is>
-          <t>CZE</t>
-        </is>
-      </c>
-      <c r="J324" t="n">
-        <v>9</v>
-      </c>
-      <c r="K324" t="n">
-        <v>323</v>
-      </c>
-      <c r="M324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="N324" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R324" t="inlineStr">
-        <is>
-          <t>SUCHANEK Daniel</t>
-        </is>
-      </c>
-      <c r="S324" t="inlineStr">
-        <is>
           <t>ROLENC Ondrej</t>
         </is>
       </c>
-      <c r="U324" t="inlineStr">
+      <c r="X319" t="inlineStr">
         <is>
           <t>42246</t>
         </is>
       </c>
-      <c r="V324" t="inlineStr">
+      <c r="Y319" t="inlineStr">
         <is>
           <t>35512</t>
         </is>
